--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549982</v>
+        <v>122550014</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519289</v>
+        <v>519079</v>
       </c>
       <c r="R2" t="n">
-        <v>6704446</v>
+        <v>6704591</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122549986</v>
+        <v>122549977</v>
       </c>
       <c r="B3" t="n">
-        <v>91264</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,28 +793,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519257</v>
+        <v>519316</v>
       </c>
       <c r="R3" t="n">
-        <v>6704453</v>
+        <v>6704456</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122550014</v>
+        <v>122549986</v>
       </c>
       <c r="B4" t="n">
-        <v>90826</v>
+        <v>91277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519079</v>
+        <v>519257</v>
       </c>
       <c r="R4" t="n">
-        <v>6704591</v>
+        <v>6704453</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549977</v>
+        <v>122549982</v>
       </c>
       <c r="B5" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,11 +1030,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519316</v>
+        <v>519289</v>
       </c>
       <c r="R5" t="n">
-        <v>6704456</v>
+        <v>6704446</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1100,6 +1100,112 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122587618</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90839</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519341</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6704445</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122550014</v>
+        <v>122549977</v>
       </c>
       <c r="B2" t="n">
         <v>90839</v>
@@ -708,7 +708,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519079</v>
+        <v>519316</v>
       </c>
       <c r="R2" t="n">
-        <v>6704591</v>
+        <v>6704456</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122549977</v>
+        <v>122550014</v>
       </c>
       <c r="B3" t="n">
         <v>90839</v>
@@ -814,11 +818,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519316</v>
+        <v>519079</v>
       </c>
       <c r="R3" t="n">
-        <v>6704456</v>
+        <v>6704591</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549986</v>
+        <v>122549982</v>
       </c>
       <c r="B4" t="n">
-        <v>91277</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519257</v>
+        <v>519289</v>
       </c>
       <c r="R4" t="n">
-        <v>6704453</v>
+        <v>6704446</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549982</v>
+        <v>122549986</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519289</v>
+        <v>519257</v>
       </c>
       <c r="R5" t="n">
-        <v>6704446</v>
+        <v>6704453</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549977</v>
+        <v>122549986</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>91278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,32 +687,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519316</v>
+        <v>519257</v>
       </c>
       <c r="R2" t="n">
-        <v>6704456</v>
+        <v>6704453</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122550014</v>
+        <v>122549977</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,7 +814,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519079</v>
+        <v>519316</v>
       </c>
       <c r="R3" t="n">
-        <v>6704591</v>
+        <v>6704456</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -894,7 +894,7 @@
         <v>122549982</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549986</v>
+        <v>122550014</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519257</v>
+        <v>519079</v>
       </c>
       <c r="R5" t="n">
-        <v>6704453</v>
+        <v>6704591</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1106,7 +1106,7 @@
         <v>122587618</v>
       </c>
       <c r="B6" t="n">
-        <v>90839</v>
+        <v>90833</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549986</v>
+        <v>122550014</v>
       </c>
       <c r="B2" t="n">
-        <v>91278</v>
+        <v>90833</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519257</v>
+        <v>519079</v>
       </c>
       <c r="R2" t="n">
-        <v>6704453</v>
+        <v>6704591</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549982</v>
+        <v>122549986</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>91278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519289</v>
+        <v>519257</v>
       </c>
       <c r="R4" t="n">
-        <v>6704446</v>
+        <v>6704453</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122550014</v>
+        <v>122549982</v>
       </c>
       <c r="B5" t="n">
         <v>90833</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519079</v>
+        <v>519289</v>
       </c>
       <c r="R5" t="n">
-        <v>6704591</v>
+        <v>6704446</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122550014</v>
+        <v>122549982</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519079</v>
+        <v>519289</v>
       </c>
       <c r="R2" t="n">
-        <v>6704591</v>
+        <v>6704446</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -784,7 +784,7 @@
         <v>122549977</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>122549986</v>
       </c>
       <c r="B4" t="n">
-        <v>91278</v>
+        <v>91279</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549982</v>
+        <v>122550014</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519289</v>
+        <v>519079</v>
       </c>
       <c r="R5" t="n">
-        <v>6704446</v>
+        <v>6704591</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1106,7 +1106,7 @@
         <v>122587618</v>
       </c>
       <c r="B6" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549982</v>
+        <v>122549977</v>
       </c>
       <c r="B2" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,7 +708,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519289</v>
+        <v>519316</v>
       </c>
       <c r="R2" t="n">
-        <v>6704446</v>
+        <v>6704456</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122549977</v>
+        <v>122549982</v>
       </c>
       <c r="B3" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,11 +818,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519316</v>
+        <v>519289</v>
       </c>
       <c r="R3" t="n">
-        <v>6704456</v>
+        <v>6704446</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -894,7 +894,7 @@
         <v>122549986</v>
       </c>
       <c r="B4" t="n">
-        <v>91279</v>
+        <v>91282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>122550014</v>
       </c>
       <c r="B5" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>122587618</v>
       </c>
       <c r="B6" t="n">
-        <v>90834</v>
+        <v>90837</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549986</v>
+        <v>122550014</v>
       </c>
       <c r="B4" t="n">
-        <v>91282</v>
+        <v>90837</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519257</v>
+        <v>519079</v>
       </c>
       <c r="R4" t="n">
-        <v>6704453</v>
+        <v>6704591</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122550014</v>
+        <v>122549986</v>
       </c>
       <c r="B5" t="n">
-        <v>90837</v>
+        <v>91282</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519079</v>
+        <v>519257</v>
       </c>
       <c r="R5" t="n">
-        <v>6704591</v>
+        <v>6704453</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1207,6 +1207,227 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122857590</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>519193</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6704543</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122857536</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98355</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>519290</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6704485</v>
+      </c>
+      <c r="S8" t="n">
+        <v>75</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122549986</v>
       </c>
       <c r="B2" t="n">
-        <v>91385</v>
+        <v>91389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122550014</v>
       </c>
       <c r="B3" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549982</v>
+        <v>122549977</v>
       </c>
       <c r="B4" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,7 +920,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -930,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519289</v>
+        <v>519316</v>
       </c>
       <c r="R4" t="n">
-        <v>6704446</v>
+        <v>6704456</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549977</v>
+        <v>122549982</v>
       </c>
       <c r="B5" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,11 +1030,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519316</v>
+        <v>519289</v>
       </c>
       <c r="R5" t="n">
-        <v>6704456</v>
+        <v>6704446</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1106,7 +1106,7 @@
         <v>122587618</v>
       </c>
       <c r="B6" t="n">
-        <v>90940</v>
+        <v>90944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122550014</v>
+        <v>122549977</v>
       </c>
       <c r="B3" t="n">
         <v>90944</v>
@@ -814,7 +814,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519079</v>
+        <v>519316</v>
       </c>
       <c r="R3" t="n">
-        <v>6704591</v>
+        <v>6704456</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549977</v>
+        <v>122549982</v>
       </c>
       <c r="B4" t="n">
         <v>90944</v>
@@ -920,11 +924,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519316</v>
+        <v>519289</v>
       </c>
       <c r="R4" t="n">
-        <v>6704456</v>
+        <v>6704446</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549982</v>
+        <v>122550014</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519289</v>
+        <v>519079</v>
       </c>
       <c r="R5" t="n">
-        <v>6704446</v>
+        <v>6704591</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122857590</v>
+        <v>122857536</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,35 +1221,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519193</v>
+        <v>519290</v>
       </c>
       <c r="R7" t="n">
-        <v>6704543</v>
+        <v>6704485</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1301,6 +1301,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122857536</v>
+        <v>122857590</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,35 +1332,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519290</v>
+        <v>519193</v>
       </c>
       <c r="R8" t="n">
-        <v>6704485</v>
+        <v>6704543</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1411,7 +1412,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549986</v>
+        <v>122549977</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519257</v>
+        <v>519316</v>
       </c>
       <c r="R2" t="n">
-        <v>6704453</v>
+        <v>6704456</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122549977</v>
+        <v>122550014</v>
       </c>
       <c r="B3" t="n">
         <v>90944</v>
@@ -814,11 +818,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519316</v>
+        <v>519079</v>
       </c>
       <c r="R3" t="n">
-        <v>6704456</v>
+        <v>6704591</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549982</v>
+        <v>122549986</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519289</v>
+        <v>519257</v>
       </c>
       <c r="R4" t="n">
-        <v>6704446</v>
+        <v>6704453</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122550014</v>
+        <v>122549982</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519079</v>
+        <v>519289</v>
       </c>
       <c r="R5" t="n">
-        <v>6704591</v>
+        <v>6704446</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122857536</v>
+        <v>122857590</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,35 +1221,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519290</v>
+        <v>519193</v>
       </c>
       <c r="R7" t="n">
-        <v>6704485</v>
+        <v>6704543</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1301,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122857590</v>
+        <v>122857536</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,35 +1331,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519193</v>
+        <v>519290</v>
       </c>
       <c r="R8" t="n">
-        <v>6704543</v>
+        <v>6704485</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1412,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549977</v>
+        <v>122549982</v>
       </c>
       <c r="B2" t="n">
         <v>90944</v>
@@ -708,11 +708,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519316</v>
+        <v>519289</v>
       </c>
       <c r="R2" t="n">
-        <v>6704456</v>
+        <v>6704446</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122550014</v>
+        <v>122549986</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>91389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519079</v>
+        <v>519257</v>
       </c>
       <c r="R3" t="n">
-        <v>6704591</v>
+        <v>6704453</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549986</v>
+        <v>122549977</v>
       </c>
       <c r="B4" t="n">
-        <v>91389</v>
+        <v>90944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,28 +899,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519257</v>
+        <v>519316</v>
       </c>
       <c r="R4" t="n">
-        <v>6704453</v>
+        <v>6704456</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122549982</v>
+        <v>122550014</v>
       </c>
       <c r="B5" t="n">
         <v>90944</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519289</v>
+        <v>519079</v>
       </c>
       <c r="R5" t="n">
-        <v>6704446</v>
+        <v>6704591</v>
       </c>
       <c r="S5" t="n">
         <v>75</v>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>122587618</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>122857536</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122857590</v>
+        <v>122857536</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,35 +1221,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519193</v>
+        <v>519290</v>
       </c>
       <c r="R7" t="n">
-        <v>6704543</v>
+        <v>6704485</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1301,6 +1301,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122857536</v>
+        <v>122857590</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>56688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,35 +1332,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519290</v>
+        <v>519193</v>
       </c>
       <c r="R8" t="n">
-        <v>6704485</v>
+        <v>6704543</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1411,7 +1412,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -1212,7 +1212,7 @@
         <v>122857536</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>122857590</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122857536</v>
+        <v>122857590</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,35 +1221,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519290</v>
+        <v>519193</v>
       </c>
       <c r="R7" t="n">
-        <v>6704485</v>
+        <v>6704543</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1301,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1320,10 +1319,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122857590</v>
+        <v>122857536</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,35 +1331,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519193</v>
+        <v>519290</v>
       </c>
       <c r="R8" t="n">
-        <v>6704543</v>
+        <v>6704485</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1412,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122857590</v>
+        <v>122857536</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,35 +1221,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519193</v>
+        <v>519290</v>
       </c>
       <c r="R7" t="n">
-        <v>6704543</v>
+        <v>6704485</v>
       </c>
       <c r="S7" t="n">
         <v>75</v>
@@ -1301,6 +1301,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122857536</v>
+        <v>122857590</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,35 +1332,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1367,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519290</v>
+        <v>519193</v>
       </c>
       <c r="R8" t="n">
-        <v>6704485</v>
+        <v>6704543</v>
       </c>
       <c r="S8" t="n">
         <v>75</v>
@@ -1411,7 +1412,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122549982</v>
+        <v>122549977</v>
       </c>
       <c r="B2" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,11 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519289</v>
+        <v>519316</v>
       </c>
       <c r="R2" t="n">
-        <v>6704446</v>
+        <v>6704456</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -781,37 +780,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122549986</v>
+        <v>122549982</v>
       </c>
       <c r="B3" t="n">
-        <v>91389</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519257</v>
+        <v>519289</v>
       </c>
       <c r="R3" t="n">
-        <v>6704453</v>
+        <v>6704446</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549977</v>
+        <v>122550014</v>
       </c>
       <c r="B4" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,11 +909,7 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519316</v>
+        <v>519079</v>
       </c>
       <c r="R4" t="n">
-        <v>6704456</v>
+        <v>6704591</v>
       </c>
       <c r="S4" t="n">
         <v>75</v>
@@ -997,15 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122550014</v>
+        <v>122587618</v>
       </c>
       <c r="B5" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,13 +1020,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519079</v>
+        <v>519341</v>
       </c>
       <c r="R5" t="n">
-        <v>6704591</v>
+        <v>6704445</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,12 +1050,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122587618</v>
+        <v>122549986</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,13 +1121,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519341</v>
+        <v>519257</v>
       </c>
       <c r="R6" t="n">
-        <v>6704445</v>
+        <v>6704453</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1151,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,12 +1187,7 @@
         <v>122857590</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,12 +1292,7 @@
         <v>122857536</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3060-2025 artfynd.xlsx
+++ b/artfynd/A 3060-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122549977</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122549982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122550014</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122587618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122549986</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122857590</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,8 +1427,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122857536</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>